--- a/docs/sample-laporan-OPS-001.xlsx
+++ b/docs/sample-laporan-OPS-001.xlsx
@@ -7,14 +7,14 @@
     <sheet sheetId="1" name="Laporan" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Laporan'!$A1:$S37</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Laporan'!$A1:$S38</definedName>
   </definedNames>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="125">
   <si>
     <t>LAPORAN HARIAN PENANGANAN GANGGUAN</t>
   </si>
@@ -174,8 +174,7 @@
     <t>Kegiatan</t>
   </si>
   <si>
-    <t xml:space="preserve">08:15 AM
-27-05-2026</t>
+    <t>08:15 AM</t>
   </si>
   <si>
     <t>010101 – ATM CAPEM IBUH PYK</t>
@@ -224,8 +223,7 @@
     <t>Listrik kembali normal, ATM online.</t>
   </si>
   <si>
-    <t xml:space="preserve">11:40 AM
-27-05-2026</t>
+    <t>11:40 AM</t>
   </si>
   <si>
     <t>010205 – ATM KANTOR KAS BUKITTINGGI</t>
@@ -268,8 +266,7 @@
     <t>ATM kembali beroperasi normal.</t>
   </si>
   <si>
-    <t xml:space="preserve">02:10 PM
-27-05-2026</t>
+    <t>02:10 PM</t>
   </si>
   <si>
     <t>020110 – JARINGAN KANTOR CABANG PAYAKUMBUH</t>
@@ -305,13 +302,13 @@
     <t>Monitoring Dilanjutkan oleh Shift berikutnya</t>
   </si>
   <si>
+    <t>Diteruskan ke shift berikutnya</t>
+  </si>
+  <si>
     <t>14:55</t>
   </si>
   <si>
     <t>Lintasarta investigasi gangguan link.</t>
-  </si>
-  <si>
-    <t>15:00</t>
   </si>
   <si>
     <r>
@@ -321,12 +318,11 @@
         <sz val="9"/>
         <rFont val="Swis721 Lt BT"/>
       </rPr>
-      <t>TINDAK LANJUT MONITORING SELANJUTNYA</t>
+      <t>Tindak lanjut monitoring selanjutnya</t>
     </r>
   </si>
   <si>
-    <t xml:space="preserve">04:05 PM
-27-05-2026</t>
+    <t>04:05 PM</t>
   </si>
   <si>
     <t>020304 – JARINGAN KANTOR CABANG SIMPANG EMPAT PASBAR</t>
@@ -359,9 +355,6 @@
     <t>Eskalasi ke NOC vendor.</t>
   </si>
   <si>
-    <t>17:30</t>
-  </si>
-  <si>
     <t>18:45</t>
   </si>
   <si>
@@ -372,9 +365,6 @@
   </si>
   <si>
     <t>Cek ulang status perangkat, jaringan masih down dan belum ada perubahan dari sisi vendor.</t>
-  </si>
-  <si>
-    <t>20:15</t>
   </si>
   <si>
     <t>Padang, 27 Mei 2026</t>
@@ -410,6 +400,9 @@
   </si>
   <si>
     <t>( Pemimpin Divisi TI )</t>
+  </si>
+  <si>
+    <t>Pimpinan</t>
   </si>
 </sst>
 </file>
@@ -527,7 +520,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -598,6 +591,9 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -985,7 +981,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:S37"/>
+  <dimension ref="B1:S38"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" defaultColWidth="10"/>
   <cols>
     <col min="1" max="1" width="2.86" customWidth="1"/>
@@ -1360,7 +1356,7 @@
       <c r="R14" s="19">
         <v>0.9968637992831542</v>
       </c>
-      <c r="S14" s="14" t="s">
+      <c r="S14" s="13" t="s">
         <v>63</v>
       </c>
     </row>
@@ -1386,7 +1382,7 @@
       <c r="P15" s="18"/>
       <c r="Q15" s="18"/>
       <c r="R15" s="19"/>
-      <c r="S15" s="14"/>
+      <c r="S15" s="13"/>
     </row>
     <row r="16" ht="20" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B16" s="13"/>
@@ -1410,7 +1406,7 @@
       <c r="P16" s="18"/>
       <c r="Q16" s="18"/>
       <c r="R16" s="19"/>
-      <c r="S16" s="14"/>
+      <c r="S16" s="13"/>
     </row>
     <row r="17" ht="20" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B17" s="13">
@@ -1464,7 +1460,7 @@
       <c r="R17" s="19">
         <v>0.9977598566308243</v>
       </c>
-      <c r="S17" s="14" t="s">
+      <c r="S17" s="13" t="s">
         <v>63</v>
       </c>
     </row>
@@ -1490,7 +1486,7 @@
       <c r="P18" s="18"/>
       <c r="Q18" s="18"/>
       <c r="R18" s="19"/>
-      <c r="S18" s="14"/>
+      <c r="S18" s="13"/>
     </row>
     <row r="19" ht="20" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B19" s="13"/>
@@ -1514,7 +1510,7 @@
       <c r="P19" s="18"/>
       <c r="Q19" s="18"/>
       <c r="R19" s="19"/>
-      <c r="S19" s="14"/>
+      <c r="S19" s="13"/>
     </row>
     <row r="20" ht="34" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B20" s="13">
@@ -1562,8 +1558,8 @@
         <v>93</v>
       </c>
       <c r="R20" s="13"/>
-      <c r="S20" s="14" t="s">
-        <v>93</v>
+      <c r="S20" s="13" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
@@ -1577,10 +1573,10 @@
       <c r="I21" s="13"/>
       <c r="J21" s="13"/>
       <c r="K21" s="20" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="L21" s="21" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="M21" s="13"/>
       <c r="N21" s="13"/>
@@ -1588,9 +1584,9 @@
       <c r="P21" s="13"/>
       <c r="Q21" s="13"/>
       <c r="R21" s="13"/>
-      <c r="S21" s="14"/>
-    </row>
-    <row r="22" ht="34" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="S21" s="13"/>
+    </row>
+    <row r="22" ht="20" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B22" s="13"/>
       <c r="C22" s="13"/>
       <c r="D22" s="14"/>
@@ -1600,9 +1596,7 @@
       <c r="H22" s="13"/>
       <c r="I22" s="13"/>
       <c r="J22" s="13"/>
-      <c r="K22" s="13" t="s">
-        <v>96</v>
-      </c>
+      <c r="K22" s="13"/>
       <c r="L22" s="22" t="s">
         <v>97</v>
       </c>
@@ -1612,7 +1606,7 @@
       <c r="P22" s="13"/>
       <c r="Q22" s="13"/>
       <c r="R22" s="13"/>
-      <c r="S22" s="14"/>
+      <c r="S22" s="13"/>
     </row>
     <row r="23" ht="62" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B23" s="13">
@@ -1660,8 +1654,8 @@
         <v>93</v>
       </c>
       <c r="R23" s="13"/>
-      <c r="S23" s="14" t="s">
-        <v>93</v>
+      <c r="S23" s="13" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="24" ht="62" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
@@ -1686,7 +1680,7 @@
       <c r="P24" s="13"/>
       <c r="Q24" s="13"/>
       <c r="R24" s="13"/>
-      <c r="S24" s="14"/>
+      <c r="S24" s="13"/>
     </row>
     <row r="25" ht="20" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B25" s="13"/>
@@ -1710,9 +1704,9 @@
       <c r="P25" s="13"/>
       <c r="Q25" s="13"/>
       <c r="R25" s="13"/>
-      <c r="S25" s="14"/>
-    </row>
-    <row r="26" ht="34" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="S25" s="13"/>
+    </row>
+    <row r="26" ht="20" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B26" s="13"/>
       <c r="C26" s="13"/>
       <c r="D26" s="14"/>
@@ -1722,9 +1716,7 @@
       <c r="H26" s="13"/>
       <c r="I26" s="13"/>
       <c r="J26" s="13"/>
-      <c r="K26" s="20" t="s">
-        <v>109</v>
-      </c>
+      <c r="K26" s="20"/>
       <c r="L26" s="21" t="s">
         <v>97</v>
       </c>
@@ -1734,7 +1726,7 @@
       <c r="P26" s="13"/>
       <c r="Q26" s="13"/>
       <c r="R26" s="13"/>
-      <c r="S26" s="14"/>
+      <c r="S26" s="13"/>
     </row>
     <row r="27" ht="62" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B27" s="13"/>
@@ -1747,10 +1739,10 @@
       <c r="I27" s="13"/>
       <c r="J27" s="13"/>
       <c r="K27" s="20" t="s">
+        <v>109</v>
+      </c>
+      <c r="L27" s="21" t="s">
         <v>110</v>
-      </c>
-      <c r="L27" s="21" t="s">
-        <v>111</v>
       </c>
       <c r="M27" s="13"/>
       <c r="N27" s="13"/>
@@ -1758,7 +1750,7 @@
       <c r="P27" s="13"/>
       <c r="Q27" s="13"/>
       <c r="R27" s="13"/>
-      <c r="S27" s="14"/>
+      <c r="S27" s="13"/>
     </row>
     <row r="28" ht="48" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B28" s="13"/>
@@ -1771,10 +1763,10 @@
       <c r="I28" s="13"/>
       <c r="J28" s="13"/>
       <c r="K28" s="20" t="s">
+        <v>111</v>
+      </c>
+      <c r="L28" s="21" t="s">
         <v>112</v>
-      </c>
-      <c r="L28" s="21" t="s">
-        <v>113</v>
       </c>
       <c r="M28" s="13"/>
       <c r="N28" s="13"/>
@@ -1782,9 +1774,9 @@
       <c r="P28" s="13"/>
       <c r="Q28" s="13"/>
       <c r="R28" s="13"/>
-      <c r="S28" s="14"/>
-    </row>
-    <row r="29" ht="34" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="S28" s="13"/>
+    </row>
+    <row r="29" ht="20" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B29" s="13"/>
       <c r="C29" s="13"/>
       <c r="D29" s="14"/>
@@ -1794,9 +1786,7 @@
       <c r="H29" s="13"/>
       <c r="I29" s="13"/>
       <c r="J29" s="13"/>
-      <c r="K29" s="13" t="s">
-        <v>114</v>
-      </c>
+      <c r="K29" s="13"/>
       <c r="L29" s="22" t="s">
         <v>97</v>
       </c>
@@ -1806,11 +1796,11 @@
       <c r="P29" s="13"/>
       <c r="Q29" s="13"/>
       <c r="R29" s="13"/>
-      <c r="S29" s="14"/>
+      <c r="S29" s="13"/>
     </row>
     <row r="31" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B31" s="23" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C31" s="23"/>
       <c r="D31" s="23"/>
@@ -1832,23 +1822,23 @@
     </row>
     <row r="32" ht="20" customHeight="1" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C32" s="24" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D32" s="24"/>
       <c r="F32" s="24" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="G32" s="24"/>
       <c r="I32" s="24" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="J32" s="24"/>
       <c r="O32" s="24" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="P32" s="24"/>
       <c r="R32" s="24" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="S32" s="24"/>
     </row>
@@ -1878,28 +1868,38 @@
     </row>
     <row r="37" ht="31" customHeight="1" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C37" s="23" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D37" s="23"/>
       <c r="F37" s="23" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="G37" s="23"/>
       <c r="I37" s="23" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="J37" s="23"/>
       <c r="O37" s="23" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="P37" s="23"/>
       <c r="R37" s="23" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="S37" s="23"/>
     </row>
+    <row r="38" ht="16" customHeight="1" spans="15:19" x14ac:dyDescent="0.25">
+      <c r="O38" s="25" t="s">
+        <v>124</v>
+      </c>
+      <c r="P38" s="25"/>
+      <c r="R38" s="25" t="s">
+        <v>124</v>
+      </c>
+      <c r="S38" s="25"/>
+    </row>
   </sheetData>
-  <mergeCells count="108">
+  <mergeCells count="110">
     <mergeCell ref="B2:R2"/>
     <mergeCell ref="B3:R3"/>
     <mergeCell ref="G5:I5"/>
@@ -2008,6 +2008,8 @@
     <mergeCell ref="I37:J37"/>
     <mergeCell ref="O37:P37"/>
     <mergeCell ref="R37:S37"/>
+    <mergeCell ref="O38:P38"/>
+    <mergeCell ref="R38:S38"/>
   </mergeCells>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
   <pageSetup orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="0"/>
